--- a/ro_workstation/data/mis/archive/20260429.xlsx
+++ b/ro_workstation/data/mis/archive/20260429.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Daily_MIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99CCDDE-7988-4038-B58E-445B750D368D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -152,7 +152,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,8 +161,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1" tint="4.9989318521683403E-2"/>
+      <color theme="1" tint="0.0499899983406067"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -192,36 +198,129 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -495,12 +594,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AM57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -619,7 +718,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="15">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -675,7 +774,7 @@
         <v>18.381734052999999</v>
       </c>
       <c r="S2" s="4">
-        <v>6.1958381999999992E-2</v>
+        <v>0.061958381999999992</v>
       </c>
       <c r="T2" s="4">
         <v>30.010468885000002</v>
@@ -738,7 +837,7 @@
         <v>0.23830370000000012</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="15">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -818,7 +917,7 @@
         <v>11659.203032899999</v>
       </c>
       <c r="AA3" s="1">
-        <v>39.14</v>
+        <v>39.140000000000001</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
@@ -827,16 +926,16 @@
         <v>0</v>
       </c>
       <c r="AD3" s="1">
-        <v>24.62</v>
+        <v>24.620000000000001</v>
       </c>
       <c r="AE3" s="1">
-        <v>63.76</v>
+        <v>63.759999999999998</v>
       </c>
       <c r="AF3" s="1">
         <v>87</v>
       </c>
       <c r="AG3" s="1">
-        <v>-23.24</v>
+        <v>-23.239999999999998</v>
       </c>
       <c r="AH3" s="1">
         <v>0</v>
@@ -857,7 +956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" ht="15">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -937,7 +1036,7 @@
         <v>5034.7058418999995</v>
       </c>
       <c r="AA4" s="1">
-        <v>24.1</v>
+        <v>24.100000000000001</v>
       </c>
       <c r="AB4" s="1">
         <v>0</v>
@@ -946,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="AD4" s="1">
-        <v>9.33</v>
+        <v>9.3300000000000001</v>
       </c>
       <c r="AE4" s="1">
         <v>33.43</v>
@@ -955,7 +1054,7 @@
         <v>35</v>
       </c>
       <c r="AG4" s="1">
-        <v>-1.57</v>
+        <v>-1.5700000000000001</v>
       </c>
       <c r="AH4" s="1">
         <v>0</v>
@@ -976,7 +1075,7 @@
         <v>0.62792000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" ht="15">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1056,7 +1155,7 @@
         <v>9291.6644751999993</v>
       </c>
       <c r="AA5" s="1">
-        <v>65.91</v>
+        <v>65.909999999999997</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
@@ -1065,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="AD5" s="1">
-        <v>3.66</v>
+        <v>3.6600000000000001</v>
       </c>
       <c r="AE5" s="1">
         <v>69.569999999999993</v>
@@ -1095,7 +1194,7 @@
         <v>0.47975000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" ht="15">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1175,7 +1274,7 @@
         <v>8732.8541217000002</v>
       </c>
       <c r="AA6" s="1">
-        <v>51.11</v>
+        <v>51.109999999999999</v>
       </c>
       <c r="AB6" s="1">
         <v>0</v>
@@ -1184,10 +1283,10 @@
         <v>0</v>
       </c>
       <c r="AD6" s="1">
-        <v>9.56</v>
+        <v>9.5600000000000005</v>
       </c>
       <c r="AE6" s="1">
-        <v>60.67</v>
+        <v>60.670000000000002</v>
       </c>
       <c r="AF6" s="1">
         <v>50</v>
@@ -1202,7 +1301,7 @@
         <v>47.432032900000003</v>
       </c>
       <c r="AJ6" s="1">
-        <v>8.8929999999999995E-2</v>
+        <v>0.088929999999999995</v>
       </c>
       <c r="AK6" s="1">
         <v>0</v>
@@ -1211,10 +1310,10 @@
         <v>0</v>
       </c>
       <c r="AM6" s="1">
-        <v>8.8929999999999995E-2</v>
+        <v>0.088929999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="15">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1306,13 +1405,13 @@
         <v>9.1300000000000008</v>
       </c>
       <c r="AE7" s="1">
-        <v>28.7</v>
+        <v>28.699999999999999</v>
       </c>
       <c r="AF7" s="1">
         <v>45</v>
       </c>
       <c r="AG7" s="1">
-        <v>-16.3</v>
+        <v>-16.300000000000001</v>
       </c>
       <c r="AH7" s="1">
         <v>0</v>
@@ -1321,7 +1420,7 @@
         <v>23.435643599999999</v>
       </c>
       <c r="AJ7" s="1">
-        <v>6.9999999999999994E-5</v>
+        <v>6.9999999999999994E-05</v>
       </c>
       <c r="AK7" s="1">
         <v>0</v>
@@ -1330,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="AM7" s="1">
-        <v>6.9999999999999994E-5</v>
+        <v>6.9999999999999994E-05</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" ht="15">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1425,7 +1524,7 @@
         <v>6.71</v>
       </c>
       <c r="AE8" s="1">
-        <v>22.94</v>
+        <v>22.940000000000001</v>
       </c>
       <c r="AF8" s="1">
         <v>35</v>
@@ -1440,7 +1539,7 @@
         <v>24.8527491</v>
       </c>
       <c r="AJ8" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.0000000000000001E-05</v>
       </c>
       <c r="AK8" s="1">
         <v>0</v>
@@ -1449,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="AM8" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.0000000000000001E-05</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" ht="15">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1550,7 +1649,7 @@
         <v>40</v>
       </c>
       <c r="AG9" s="1">
-        <v>-5.93</v>
+        <v>-5.9299999999999997</v>
       </c>
       <c r="AH9" s="1">
         <v>0</v>
@@ -1559,7 +1658,7 @@
         <v>38.598376799999997</v>
       </c>
       <c r="AJ9" s="1">
-        <v>1.359E-2</v>
+        <v>0.01359</v>
       </c>
       <c r="AK9" s="1">
         <v>0</v>
@@ -1568,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="AM9" s="1">
-        <v>1.359E-2</v>
+        <v>0.01359</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" ht="15">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1651,25 +1750,25 @@
         <v>15660.983626800002</v>
       </c>
       <c r="AA10" s="1">
-        <v>32.71</v>
+        <v>32.710000000000001</v>
       </c>
       <c r="AB10" s="1">
-        <v>24.44</v>
+        <v>24.440000000000001</v>
       </c>
       <c r="AC10" s="1">
         <v>0</v>
       </c>
       <c r="AD10" s="1">
-        <v>31.74</v>
+        <v>31.739999999999998</v>
       </c>
       <c r="AE10" s="1">
-        <v>88.89</v>
+        <v>88.890000000000001</v>
       </c>
       <c r="AF10" s="1">
         <v>80</v>
       </c>
       <c r="AG10" s="1">
-        <v>8.89</v>
+        <v>8.8900000000000006</v>
       </c>
       <c r="AH10" s="1">
         <v>0</v>
@@ -1690,7 +1789,7 @@
         <v>17.575610000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" ht="15">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1770,7 +1869,7 @@
         <v>10234.4161272</v>
       </c>
       <c r="AA11" s="1">
-        <v>259.58</v>
+        <v>259.57999999999998</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
@@ -1779,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="1">
-        <v>21.83</v>
+        <v>21.829999999999998</v>
       </c>
       <c r="AE11" s="1">
         <v>281.41000000000003</v>
@@ -1809,7 +1908,7 @@
         <v>1.1543399999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" ht="15">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1889,7 +1988,7 @@
         <v>7967.545185500001</v>
       </c>
       <c r="AA12" s="1">
-        <v>7.43</v>
+        <v>7.4299999999999997</v>
       </c>
       <c r="AB12" s="1">
         <v>0</v>
@@ -1898,16 +1997,16 @@
         <v>0</v>
       </c>
       <c r="AD12" s="1">
-        <v>6.37</v>
+        <v>6.3700000000000001</v>
       </c>
       <c r="AE12" s="1">
-        <v>13.8</v>
+        <v>13.800000000000001</v>
       </c>
       <c r="AF12" s="1">
         <v>35</v>
       </c>
       <c r="AG12" s="1">
-        <v>-21.2</v>
+        <v>-21.199999999999999</v>
       </c>
       <c r="AH12" s="1">
         <v>0</v>
@@ -1928,7 +2027,7 @@
         <v>2.18662</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" ht="15">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -2008,7 +2107,7 @@
         <v>4649.6843283999997</v>
       </c>
       <c r="AA13" s="1">
-        <v>41.1</v>
+        <v>41.100000000000001</v>
       </c>
       <c r="AB13" s="1">
         <v>0</v>
@@ -2020,13 +2119,13 @@
         <v>16.190000000000001</v>
       </c>
       <c r="AE13" s="1">
-        <v>57.29</v>
+        <v>57.289999999999999</v>
       </c>
       <c r="AF13" s="1">
         <v>30</v>
       </c>
       <c r="AG13" s="1">
-        <v>27.29</v>
+        <v>27.289999999999999</v>
       </c>
       <c r="AH13" s="1">
         <v>0</v>
@@ -2035,7 +2134,7 @@
         <v>23.497233399999999</v>
       </c>
       <c r="AJ13" s="1">
-        <v>9.6000000000000002E-4</v>
+        <v>0.00096000000000000002</v>
       </c>
       <c r="AK13" s="1">
         <v>0</v>
@@ -2044,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="AM13" s="1">
-        <v>9.6000000000000002E-4</v>
+        <v>0.00096000000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" ht="15">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -2130,7 +2229,7 @@
         <v>35.909999999999997</v>
       </c>
       <c r="AB14" s="1">
-        <v>6.63</v>
+        <v>6.6299999999999999</v>
       </c>
       <c r="AC14" s="1">
         <v>0</v>
@@ -2139,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="AE14" s="1">
-        <v>42.54</v>
+        <v>42.539999999999999</v>
       </c>
       <c r="AF14" s="1">
         <v>30</v>
       </c>
       <c r="AG14" s="1">
-        <v>12.54</v>
+        <v>12.539999999999999</v>
       </c>
       <c r="AH14" s="1">
         <v>0</v>
@@ -2154,7 +2253,7 @@
         <v>29.416207</v>
       </c>
       <c r="AJ14" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK14" s="1">
         <v>0</v>
@@ -2163,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="AM14" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" ht="15">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -2246,7 +2345,7 @@
         <v>5877.7050895000002</v>
       </c>
       <c r="AA15" s="1">
-        <v>32.42</v>
+        <v>32.420000000000002</v>
       </c>
       <c r="AB15" s="1">
         <v>0</v>
@@ -2255,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="AD15" s="1">
-        <v>2.94</v>
+        <v>2.9399999999999999</v>
       </c>
       <c r="AE15" s="1">
-        <v>35.36</v>
+        <v>35.359999999999999</v>
       </c>
       <c r="AF15" s="1">
         <v>30</v>
       </c>
       <c r="AG15" s="1">
-        <v>5.36</v>
+        <v>5.3600000000000003</v>
       </c>
       <c r="AH15" s="1">
         <v>400</v>
@@ -2273,7 +2372,7 @@
         <v>33.466878399999999</v>
       </c>
       <c r="AJ15" s="1">
-        <v>8.1999999999999998E-4</v>
+        <v>0.00081999999999999998</v>
       </c>
       <c r="AK15" s="1">
         <v>0</v>
@@ -2282,10 +2381,10 @@
         <v>0</v>
       </c>
       <c r="AM15" s="1">
-        <v>8.1999999999999998E-4</v>
+        <v>0.00081999999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" ht="15">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -2365,7 +2464,7 @@
         <v>12317.436464500001</v>
       </c>
       <c r="AA16" s="1">
-        <v>46.76</v>
+        <v>46.759999999999998</v>
       </c>
       <c r="AB16" s="1">
         <v>0</v>
@@ -2377,13 +2476,13 @@
         <v>9.5500000000000007</v>
       </c>
       <c r="AE16" s="1">
-        <v>56.31</v>
+        <v>56.310000000000002</v>
       </c>
       <c r="AF16" s="1">
         <v>33</v>
       </c>
       <c r="AG16" s="1">
-        <v>23.31</v>
+        <v>23.309999999999999</v>
       </c>
       <c r="AH16" s="1">
         <v>0</v>
@@ -2404,7 +2503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2484,7 +2583,7 @@
         <v>9686.7306611000004</v>
       </c>
       <c r="AA17" s="1">
-        <v>23.83</v>
+        <v>23.829999999999998</v>
       </c>
       <c r="AB17" s="1">
         <v>0</v>
@@ -2493,16 +2592,16 @@
         <v>0</v>
       </c>
       <c r="AD17" s="1">
-        <v>3.43</v>
+        <v>3.4300000000000002</v>
       </c>
       <c r="AE17" s="1">
-        <v>27.26</v>
+        <v>27.260000000000002</v>
       </c>
       <c r="AF17" s="1">
         <v>35</v>
       </c>
       <c r="AG17" s="1">
-        <v>-7.74</v>
+        <v>-7.7400000000000002</v>
       </c>
       <c r="AH17" s="1">
         <v>0</v>
@@ -2523,7 +2622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2603,7 +2702,7 @@
         <v>3295.3886017999998</v>
       </c>
       <c r="AA18" s="1">
-        <v>22.12</v>
+        <v>22.120000000000001</v>
       </c>
       <c r="AB18" s="1">
         <v>0</v>
@@ -2615,13 +2714,13 @@
         <v>0</v>
       </c>
       <c r="AE18" s="1">
-        <v>22.12</v>
+        <v>22.120000000000001</v>
       </c>
       <c r="AF18" s="1">
         <v>25</v>
       </c>
       <c r="AG18" s="1">
-        <v>-2.88</v>
+        <v>-2.8799999999999999</v>
       </c>
       <c r="AH18" s="1">
         <v>0</v>
@@ -2630,7 +2729,7 @@
         <v>17.3534009</v>
       </c>
       <c r="AJ18" s="1">
-        <v>9.2000000000000003E-4</v>
+        <v>0.00092000000000000003</v>
       </c>
       <c r="AK18" s="1">
         <v>0</v>
@@ -2639,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="AM18" s="1">
-        <v>9.2000000000000003E-4</v>
+        <v>0.00092000000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2740,7 +2839,7 @@
         <v>25</v>
       </c>
       <c r="AG19" s="1">
-        <v>-3.93</v>
+        <v>-3.9300000000000002</v>
       </c>
       <c r="AH19" s="1">
         <v>0</v>
@@ -2749,7 +2848,7 @@
         <v>24.442581799999999</v>
       </c>
       <c r="AJ19" s="1">
-        <v>3.6000000000000002E-4</v>
+        <v>0.00036000000000000002</v>
       </c>
       <c r="AK19" s="1">
         <v>0</v>
@@ -2758,10 +2857,10 @@
         <v>0</v>
       </c>
       <c r="AM19" s="1">
-        <v>3.6000000000000002E-4</v>
+        <v>0.00036000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2841,7 +2940,7 @@
         <v>7072.7572256000003</v>
       </c>
       <c r="AA20" s="1">
-        <v>67.42</v>
+        <v>67.420000000000002</v>
       </c>
       <c r="AB20" s="1">
         <v>0</v>
@@ -2853,13 +2952,13 @@
         <v>14.74</v>
       </c>
       <c r="AE20" s="1">
-        <v>82.16</v>
+        <v>82.159999999999997</v>
       </c>
       <c r="AF20" s="1">
         <v>30</v>
       </c>
       <c r="AG20" s="1">
-        <v>52.16</v>
+        <v>52.159999999999997</v>
       </c>
       <c r="AH20" s="1">
         <v>0</v>
@@ -2880,7 +2979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2972,7 +3071,7 @@
         <v>4.8099999999999996</v>
       </c>
       <c r="AE21" s="1">
-        <v>27.54</v>
+        <v>27.539999999999999</v>
       </c>
       <c r="AF21" s="1">
         <v>30</v>
@@ -2987,7 +3086,7 @@
         <v>21.5228495</v>
       </c>
       <c r="AJ21" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK21" s="1">
         <v>0</v>
@@ -2996,10 +3095,10 @@
         <v>0</v>
       </c>
       <c r="AM21" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3079,7 +3178,7 @@
         <v>5570.4262413000006</v>
       </c>
       <c r="AA22" s="1">
-        <v>67.12</v>
+        <v>67.120000000000005</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -3088,10 +3187,10 @@
         <v>0</v>
       </c>
       <c r="AD22" s="1">
-        <v>9.61</v>
+        <v>9.6099999999999994</v>
       </c>
       <c r="AE22" s="1">
-        <v>76.73</v>
+        <v>76.730000000000004</v>
       </c>
       <c r="AF22" s="1">
         <v>60</v>
@@ -3106,7 +3205,7 @@
         <v>36.3992401</v>
       </c>
       <c r="AJ22" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK22" s="1">
         <v>0</v>
@@ -3115,10 +3214,10 @@
         <v>0</v>
       </c>
       <c r="AM22" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3207,16 +3306,16 @@
         <v>0</v>
       </c>
       <c r="AD23" s="1">
-        <v>31.71</v>
+        <v>31.710000000000001</v>
       </c>
       <c r="AE23" s="1">
-        <v>61.14</v>
+        <v>61.140000000000001</v>
       </c>
       <c r="AF23" s="1">
         <v>70</v>
       </c>
       <c r="AG23" s="1">
-        <v>-8.86</v>
+        <v>-8.8599999999999994</v>
       </c>
       <c r="AH23" s="1">
         <v>0</v>
@@ -3225,7 +3324,7 @@
         <v>54.387809699999998</v>
       </c>
       <c r="AJ23" s="1">
-        <v>8.9319999999999997E-2</v>
+        <v>0.089319999999999997</v>
       </c>
       <c r="AK23" s="1">
         <v>0</v>
@@ -3234,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="AM23" s="1">
-        <v>8.9319999999999997E-2</v>
+        <v>0.089319999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3329,13 +3428,13 @@
         <v>0</v>
       </c>
       <c r="AE24" s="1">
-        <v>22.1</v>
+        <v>22.100000000000001</v>
       </c>
       <c r="AF24" s="1">
         <v>45</v>
       </c>
       <c r="AG24" s="1">
-        <v>-22.9</v>
+        <v>-22.899999999999999</v>
       </c>
       <c r="AH24" s="1">
         <v>0</v>
@@ -3344,7 +3443,7 @@
         <v>25.038706300000001</v>
       </c>
       <c r="AJ24" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>0.00055000000000000003</v>
       </c>
       <c r="AK24" s="1">
         <v>0</v>
@@ -3353,10 +3452,10 @@
         <v>0</v>
       </c>
       <c r="AM24" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>0.00055000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3436,7 +3535,7 @@
         <v>3310.8299339</v>
       </c>
       <c r="AA25" s="1">
-        <v>12.7</v>
+        <v>12.699999999999999</v>
       </c>
       <c r="AB25" s="1">
         <v>0</v>
@@ -3448,7 +3547,7 @@
         <v>10.33</v>
       </c>
       <c r="AE25" s="1">
-        <v>23.03</v>
+        <v>23.030000000000001</v>
       </c>
       <c r="AF25" s="1">
         <v>25</v>
@@ -3463,7 +3562,7 @@
         <v>10.3883043</v>
       </c>
       <c r="AJ25" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="AK25" s="1">
         <v>0</v>
@@ -3472,10 +3571,10 @@
         <v>0</v>
       </c>
       <c r="AM25" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>0.0030000000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3594,7 +3693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3686,13 +3785,13 @@
         <v>10.98</v>
       </c>
       <c r="AE27" s="1">
-        <v>33.64</v>
+        <v>33.640000000000001</v>
       </c>
       <c r="AF27" s="1">
         <v>36</v>
       </c>
       <c r="AG27" s="1">
-        <v>-2.36</v>
+        <v>-2.3599999999999999</v>
       </c>
       <c r="AH27" s="1">
         <v>0</v>
@@ -3701,7 +3800,7 @@
         <v>32.970147699999998</v>
       </c>
       <c r="AJ27" s="1">
-        <v>5.0000000000000001E-4</v>
+        <v>0.00050000000000000001</v>
       </c>
       <c r="AK27" s="1">
         <v>0</v>
@@ -3710,10 +3809,10 @@
         <v>0</v>
       </c>
       <c r="AM27" s="1">
-        <v>5.0000000000000001E-4</v>
+        <v>0.00050000000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3793,7 +3892,7 @@
         <v>6775.8769065999995</v>
       </c>
       <c r="AA28" s="1">
-        <v>30.62</v>
+        <v>30.620000000000001</v>
       </c>
       <c r="AB28" s="1">
         <v>0</v>
@@ -3802,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="AD28" s="1">
-        <v>2.31</v>
+        <v>2.3100000000000001</v>
       </c>
       <c r="AE28" s="1">
         <v>32.93</v>
@@ -3811,7 +3910,7 @@
         <v>30</v>
       </c>
       <c r="AG28" s="1">
-        <v>2.93</v>
+        <v>2.9300000000000002</v>
       </c>
       <c r="AH28" s="1">
         <v>0</v>
@@ -3820,7 +3919,7 @@
         <v>33.650841200000002</v>
       </c>
       <c r="AJ28" s="1">
-        <v>4.3800000000000002E-3</v>
+        <v>0.0043800000000000002</v>
       </c>
       <c r="AK28" s="1">
         <v>0</v>
@@ -3829,10 +3928,10 @@
         <v>0</v>
       </c>
       <c r="AM28" s="1">
-        <v>4.3800000000000002E-3</v>
+        <v>0.0043800000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3912,7 +4011,7 @@
         <v>8655.7645848000011</v>
       </c>
       <c r="AA29" s="1">
-        <v>53.88</v>
+        <v>53.880000000000003</v>
       </c>
       <c r="AB29" s="1">
         <v>17.809999999999999</v>
@@ -3921,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="1">
-        <v>5.57</v>
+        <v>5.5700000000000003</v>
       </c>
       <c r="AE29" s="1">
         <v>77.260000000000005</v>
@@ -3930,7 +4029,7 @@
         <v>40</v>
       </c>
       <c r="AG29" s="1">
-        <v>37.26</v>
+        <v>37.259999999999998</v>
       </c>
       <c r="AH29" s="1">
         <v>0</v>
@@ -3951,7 +4050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4034,7 +4133,7 @@
         <v>28</v>
       </c>
       <c r="AB30" s="1">
-        <v>7.86</v>
+        <v>7.8600000000000003</v>
       </c>
       <c r="AC30" s="1">
         <v>0</v>
@@ -4043,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="AE30" s="1">
-        <v>35.86</v>
+        <v>35.859999999999999</v>
       </c>
       <c r="AF30" s="1">
         <v>40</v>
@@ -4070,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4150,7 +4249,7 @@
         <v>7123.0296542000006</v>
       </c>
       <c r="AA31" s="1">
-        <v>21.1</v>
+        <v>21.100000000000001</v>
       </c>
       <c r="AB31" s="1">
         <v>0</v>
@@ -4159,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="AD31" s="1">
-        <v>2.92</v>
+        <v>2.9199999999999999</v>
       </c>
       <c r="AE31" s="1">
         <v>24.02</v>
@@ -4168,7 +4267,7 @@
         <v>30</v>
       </c>
       <c r="AG31" s="1">
-        <v>-5.98</v>
+        <v>-5.9800000000000004</v>
       </c>
       <c r="AH31" s="1">
         <v>0</v>
@@ -4177,7 +4276,7 @@
         <v>33.732950500000001</v>
       </c>
       <c r="AJ31" s="1">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AK31" s="1">
         <v>0</v>
@@ -4186,10 +4285,10 @@
         <v>0</v>
       </c>
       <c r="AM31" s="1">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4269,7 +4368,7 @@
         <v>6221.5379241000001</v>
       </c>
       <c r="AA32" s="1">
-        <v>24.51</v>
+        <v>24.510000000000002</v>
       </c>
       <c r="AB32" s="1">
         <v>0</v>
@@ -4281,7 +4380,7 @@
         <v>15.35</v>
       </c>
       <c r="AE32" s="1">
-        <v>39.86</v>
+        <v>39.859999999999999</v>
       </c>
       <c r="AF32" s="1">
         <v>35</v>
@@ -4308,7 +4407,7 @@
         <v>0.50927</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="15">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4388,7 +4487,7 @@
         <v>13162.222746399999</v>
       </c>
       <c r="AA33" s="1">
-        <v>61.74</v>
+        <v>61.740000000000002</v>
       </c>
       <c r="AB33" s="1">
         <v>0</v>
@@ -4397,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="AD33" s="1">
-        <v>6.22</v>
+        <v>6.2199999999999998</v>
       </c>
       <c r="AE33" s="1">
         <v>67.959999999999994</v>
@@ -4406,7 +4505,7 @@
         <v>43</v>
       </c>
       <c r="AG33" s="1">
-        <v>24.96</v>
+        <v>24.960000000000001</v>
       </c>
       <c r="AH33" s="1">
         <v>0</v>
@@ -4415,7 +4514,7 @@
         <v>36.303210399999998</v>
       </c>
       <c r="AJ33" s="1">
-        <v>8.8999999999999995E-4</v>
+        <v>0.00088999999999999995</v>
       </c>
       <c r="AK33" s="1">
         <v>0</v>
@@ -4424,10 +4523,10 @@
         <v>0</v>
       </c>
       <c r="AM33" s="1">
-        <v>8.8999999999999995E-4</v>
+        <v>0.00088999999999999995</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="15">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4510,7 +4609,7 @@
         <v>8.2899999999999991</v>
       </c>
       <c r="AB34" s="1">
-        <v>7.32</v>
+        <v>7.3200000000000003</v>
       </c>
       <c r="AC34" s="1">
         <v>0</v>
@@ -4519,13 +4618,13 @@
         <v>10.85</v>
       </c>
       <c r="AE34" s="1">
-        <v>26.46</v>
+        <v>26.460000000000001</v>
       </c>
       <c r="AF34" s="1">
         <v>55</v>
       </c>
       <c r="AG34" s="1">
-        <v>-28.54</v>
+        <v>-28.539999999999999</v>
       </c>
       <c r="AH34" s="1">
         <v>0</v>
@@ -4534,7 +4633,7 @@
         <v>38.178152400000002</v>
       </c>
       <c r="AJ34" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK34" s="1">
         <v>0</v>
@@ -4543,10 +4642,10 @@
         <v>0</v>
       </c>
       <c r="AM34" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="15">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4599,7 +4698,7 @@
         <v>286.5601987</v>
       </c>
       <c r="R35" s="3">
-        <v>3.1</v>
+        <v>3.1000000000000001</v>
       </c>
       <c r="S35" s="3">
         <v>0.91666669999999995</v>
@@ -4626,7 +4725,7 @@
         <v>7317.6749250000003</v>
       </c>
       <c r="AA35" s="1">
-        <v>12.89</v>
+        <v>12.890000000000001</v>
       </c>
       <c r="AB35" s="1">
         <v>0</v>
@@ -4635,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="AD35" s="1">
-        <v>5.88</v>
+        <v>5.8799999999999999</v>
       </c>
       <c r="AE35" s="1">
         <v>18.77</v>
@@ -4644,7 +4743,7 @@
         <v>28</v>
       </c>
       <c r="AG35" s="1">
-        <v>-9.23</v>
+        <v>-9.2300000000000004</v>
       </c>
       <c r="AH35" s="1">
         <v>0</v>
@@ -4665,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="15">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4745,7 +4844,7 @@
         <v>6940.3839117999996</v>
       </c>
       <c r="AA36" s="1">
-        <v>36.72</v>
+        <v>36.719999999999999</v>
       </c>
       <c r="AB36" s="1">
         <v>0</v>
@@ -4754,16 +4853,16 @@
         <v>0</v>
       </c>
       <c r="AD36" s="1">
-        <v>14.39</v>
+        <v>14.390000000000001</v>
       </c>
       <c r="AE36" s="1">
-        <v>51.11</v>
+        <v>51.109999999999999</v>
       </c>
       <c r="AF36" s="1">
         <v>33</v>
       </c>
       <c r="AG36" s="1">
-        <v>18.11</v>
+        <v>18.109999999999999</v>
       </c>
       <c r="AH36" s="1">
         <v>0</v>
@@ -4772,7 +4871,7 @@
         <v>30.269842400000002</v>
       </c>
       <c r="AJ36" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK36" s="1">
         <v>0</v>
@@ -4781,10 +4880,10 @@
         <v>0</v>
       </c>
       <c r="AM36" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="15">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4864,7 +4963,7 @@
         <v>10964.976055699999</v>
       </c>
       <c r="AA37" s="1">
-        <v>32.1</v>
+        <v>32.100000000000001</v>
       </c>
       <c r="AB37" s="1">
         <v>0</v>
@@ -4873,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="AD37" s="1">
-        <v>5.74</v>
+        <v>5.7400000000000002</v>
       </c>
       <c r="AE37" s="1">
         <v>37.840000000000003</v>
@@ -4882,7 +4981,7 @@
         <v>34</v>
       </c>
       <c r="AG37" s="1">
-        <v>3.84</v>
+        <v>3.8399999999999999</v>
       </c>
       <c r="AH37" s="1">
         <v>0</v>
@@ -4891,7 +4990,7 @@
         <v>35.781134299999998</v>
       </c>
       <c r="AJ37" s="1">
-        <v>1.546E-2</v>
+        <v>0.01546</v>
       </c>
       <c r="AK37" s="1">
         <v>0</v>
@@ -4900,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="AM37" s="1">
-        <v>1.546E-2</v>
+        <v>0.01546</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="15">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -4983,7 +5082,7 @@
         <v>7528.7141868000008</v>
       </c>
       <c r="AA38" s="1">
-        <v>40.53</v>
+        <v>40.530000000000001</v>
       </c>
       <c r="AB38" s="1">
         <v>0</v>
@@ -4992,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="AD38" s="1">
-        <v>7.22</v>
+        <v>7.2199999999999998</v>
       </c>
       <c r="AE38" s="1">
         <v>47.75</v>
@@ -5010,7 +5109,7 @@
         <v>31.5109809</v>
       </c>
       <c r="AJ38" s="1">
-        <v>2.0920000000000001E-2</v>
+        <v>0.020920000000000001</v>
       </c>
       <c r="AK38" s="1">
         <v>0</v>
@@ -5019,10 +5118,10 @@
         <v>0</v>
       </c>
       <c r="AM38" s="1">
-        <v>2.0920000000000001E-2</v>
+        <v>0.020920000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="15">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -5102,7 +5201,7 @@
         <v>12740.6149052</v>
       </c>
       <c r="AA39" s="1">
-        <v>45.08</v>
+        <v>45.079999999999998</v>
       </c>
       <c r="AB39" s="1">
         <v>0</v>
@@ -5111,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AD39" s="1">
-        <v>-4.12</v>
+        <v>-4.1200000000000001</v>
       </c>
       <c r="AE39" s="1">
-        <v>40.96</v>
+        <v>40.960000000000001</v>
       </c>
       <c r="AF39" s="1">
         <v>38</v>
@@ -5141,7 +5240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="15">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5194,7 +5293,7 @@
         <v>31.9037273</v>
       </c>
       <c r="R40" s="3">
-        <v>0.32</v>
+        <v>0.32000000000000001</v>
       </c>
       <c r="S40" s="3">
         <v>0</v>
@@ -5221,7 +5320,7 @@
         <v>8817.8033483999989</v>
       </c>
       <c r="AA40" s="1">
-        <v>39.28</v>
+        <v>39.280000000000001</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
@@ -5230,16 +5329,16 @@
         <v>0</v>
       </c>
       <c r="AD40" s="1">
-        <v>10.36</v>
+        <v>10.359999999999999</v>
       </c>
       <c r="AE40" s="1">
-        <v>49.64</v>
+        <v>49.640000000000001</v>
       </c>
       <c r="AF40" s="1">
         <v>35</v>
       </c>
       <c r="AG40" s="1">
-        <v>14.64</v>
+        <v>14.640000000000001</v>
       </c>
       <c r="AH40" s="1">
         <v>0</v>
@@ -5260,7 +5359,7 @@
         <v>1.01376</v>
       </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="15">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5340,7 +5439,7 @@
         <v>4616.6720822000007</v>
       </c>
       <c r="AA41" s="1">
-        <v>46.98</v>
+        <v>46.979999999999997</v>
       </c>
       <c r="AB41" s="1">
         <v>0</v>
@@ -5349,16 +5448,16 @@
         <v>0</v>
       </c>
       <c r="AD41" s="1">
-        <v>9.39</v>
+        <v>9.3900000000000006</v>
       </c>
       <c r="AE41" s="1">
-        <v>56.37</v>
+        <v>56.369999999999997</v>
       </c>
       <c r="AF41" s="1">
         <v>33</v>
       </c>
       <c r="AG41" s="1">
-        <v>23.37</v>
+        <v>23.370000000000001</v>
       </c>
       <c r="AH41" s="1">
         <v>0</v>
@@ -5367,7 +5466,7 @@
         <v>19.027186499999999</v>
       </c>
       <c r="AJ41" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK41" s="1">
         <v>0</v>
@@ -5376,10 +5475,10 @@
         <v>0</v>
       </c>
       <c r="AM41" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="15">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -5462,7 +5561,7 @@
         <v>10.1</v>
       </c>
       <c r="AB42" s="1">
-        <v>21.85</v>
+        <v>21.850000000000001</v>
       </c>
       <c r="AC42" s="1">
         <v>0</v>
@@ -5471,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="AE42" s="1">
-        <v>31.95</v>
+        <v>31.949999999999999</v>
       </c>
       <c r="AF42" s="1">
         <v>34</v>
@@ -5498,7 +5597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="15">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5578,7 +5677,7 @@
         <v>11388.6727089</v>
       </c>
       <c r="AA43" s="1">
-        <v>62.98</v>
+        <v>62.979999999999997</v>
       </c>
       <c r="AB43" s="1">
         <v>0</v>
@@ -5590,7 +5689,7 @@
         <v>3.04</v>
       </c>
       <c r="AE43" s="1">
-        <v>66.02</v>
+        <v>66.019999999999996</v>
       </c>
       <c r="AF43" s="1">
         <v>30</v>
@@ -5617,7 +5716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="15">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5670,7 +5769,7 @@
         <v>72.0901748</v>
       </c>
       <c r="R44" s="3">
-        <v>2.8</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -5697,7 +5796,7 @@
         <v>4473.5962675000001</v>
       </c>
       <c r="AA44" s="1">
-        <v>16.79</v>
+        <v>16.789999999999999</v>
       </c>
       <c r="AB44" s="1">
         <v>0</v>
@@ -5706,10 +5805,10 @@
         <v>0</v>
       </c>
       <c r="AD44" s="1">
-        <v>2.17</v>
+        <v>2.1699999999999999</v>
       </c>
       <c r="AE44" s="1">
-        <v>18.96</v>
+        <v>18.960000000000001</v>
       </c>
       <c r="AF44" s="1">
         <v>25</v>
@@ -5724,7 +5823,7 @@
         <v>13.6677254</v>
       </c>
       <c r="AJ44" s="1">
-        <v>4.0000000000000001E-3</v>
+        <v>0.0040000000000000001</v>
       </c>
       <c r="AK44" s="1">
         <v>0</v>
@@ -5733,10 +5832,10 @@
         <v>0</v>
       </c>
       <c r="AM44" s="1">
-        <v>4.0000000000000001E-3</v>
+        <v>0.0040000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="15">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5816,7 +5915,7 @@
         <v>9848.9959178999998</v>
       </c>
       <c r="AA45" s="1">
-        <v>9.98</v>
+        <v>9.9800000000000004</v>
       </c>
       <c r="AB45" s="1">
         <v>0</v>
@@ -5825,10 +5924,10 @@
         <v>0</v>
       </c>
       <c r="AD45" s="1">
-        <v>14.37</v>
+        <v>14.369999999999999</v>
       </c>
       <c r="AE45" s="1">
-        <v>24.35</v>
+        <v>24.350000000000001</v>
       </c>
       <c r="AF45" s="1">
         <v>40</v>
@@ -5855,7 +5954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="15">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -5944,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="AD46" s="1">
-        <v>6.09</v>
+        <v>6.0899999999999999</v>
       </c>
       <c r="AE46" s="1">
         <v>20.68</v>
@@ -5974,7 +6073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="15">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -6063,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="1">
-        <v>7.35</v>
+        <v>7.3499999999999996</v>
       </c>
       <c r="AE47" s="1">
-        <v>32.78</v>
+        <v>32.780000000000001</v>
       </c>
       <c r="AF47" s="1">
         <v>35</v>
@@ -6093,7 +6192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="15">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -6173,7 +6272,7 @@
         <v>8038.5568235999999</v>
       </c>
       <c r="AA48" s="1">
-        <v>26.72</v>
+        <v>26.719999999999999</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
@@ -6182,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="AD48" s="1">
-        <v>6.23</v>
+        <v>6.2300000000000004</v>
       </c>
       <c r="AE48" s="1">
         <v>32.950000000000003</v>
@@ -6191,7 +6290,7 @@
         <v>27</v>
       </c>
       <c r="AG48" s="1">
-        <v>5.95</v>
+        <v>5.9500000000000002</v>
       </c>
       <c r="AH48" s="1">
         <v>0</v>
@@ -6200,7 +6299,7 @@
         <v>29.6220742</v>
       </c>
       <c r="AJ48" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK48" s="1">
         <v>0</v>
@@ -6209,10 +6308,10 @@
         <v>0</v>
       </c>
       <c r="AM48" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -6331,7 +6430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -6411,7 +6510,7 @@
         <v>3187.4200154</v>
       </c>
       <c r="AA50" s="1">
-        <v>23.39</v>
+        <v>23.390000000000001</v>
       </c>
       <c r="AB50" s="1">
         <v>0</v>
@@ -6420,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AD50" s="1">
-        <v>3.12</v>
+        <v>3.1200000000000001</v>
       </c>
       <c r="AE50" s="1">
-        <v>26.51</v>
+        <v>26.510000000000002</v>
       </c>
       <c r="AF50" s="1">
         <v>15</v>
@@ -6450,7 +6549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -6530,7 +6629,7 @@
         <v>5047.5478720000001</v>
       </c>
       <c r="AA51" s="1">
-        <v>22.12</v>
+        <v>22.120000000000001</v>
       </c>
       <c r="AB51" s="1">
         <v>0</v>
@@ -6539,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="AD51" s="1">
-        <v>3.61</v>
+        <v>3.6099999999999999</v>
       </c>
       <c r="AE51" s="1">
         <v>25.73</v>
@@ -6548,7 +6647,7 @@
         <v>25</v>
       </c>
       <c r="AG51" s="1">
-        <v>0.73</v>
+        <v>0.72999999999999998</v>
       </c>
       <c r="AH51" s="1">
         <v>0</v>
@@ -6569,7 +6668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -6649,7 +6748,7 @@
         <v>2994.5723794999999</v>
       </c>
       <c r="AA52" s="1">
-        <v>68.37</v>
+        <v>68.370000000000005</v>
       </c>
       <c r="AB52" s="1">
         <v>0</v>
@@ -6658,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="AD52" s="1">
-        <v>8.56</v>
+        <v>8.5600000000000005</v>
       </c>
       <c r="AE52" s="1">
         <v>76.930000000000007</v>
@@ -6676,7 +6775,7 @@
         <v>8.8763623999999997</v>
       </c>
       <c r="AJ52" s="1">
-        <v>3.32E-2</v>
+        <v>0.0332</v>
       </c>
       <c r="AK52" s="1">
         <v>0</v>
@@ -6685,10 +6784,10 @@
         <v>0</v>
       </c>
       <c r="AM52" s="1">
-        <v>3.32E-2</v>
+        <v>0.0332</v>
       </c>
     </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -6768,7 +6867,7 @@
         <v>6501.0712792000004</v>
       </c>
       <c r="AA53" s="1">
-        <v>32.47</v>
+        <v>32.469999999999999</v>
       </c>
       <c r="AB53" s="1">
         <v>0</v>
@@ -6807,7 +6906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6887,7 +6986,7 @@
         <v>6119.0906046</v>
       </c>
       <c r="AA54" s="1">
-        <v>16.36</v>
+        <v>16.359999999999999</v>
       </c>
       <c r="AB54" s="1">
         <v>0</v>
@@ -6899,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="AE54" s="1">
-        <v>16.36</v>
+        <v>16.359999999999999</v>
       </c>
       <c r="AF54" s="1">
         <v>23</v>
       </c>
       <c r="AG54" s="1">
-        <v>-6.64</v>
+        <v>-6.6399999999999997</v>
       </c>
       <c r="AH54" s="1">
         <v>0</v>
@@ -6926,7 +7025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -7006,7 +7105,7 @@
         <v>4284.5586997999999</v>
       </c>
       <c r="AA55" s="1">
-        <v>21.85</v>
+        <v>21.850000000000001</v>
       </c>
       <c r="AB55" s="1">
         <v>0</v>
@@ -7024,7 +7123,7 @@
         <v>23</v>
       </c>
       <c r="AG55" s="1">
-        <v>1.32</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="AH55" s="1">
         <v>0</v>
@@ -7045,7 +7144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -7062,7 +7161,7 @@
         <v>975.31999319999989</v>
       </c>
       <c r="F56" s="3">
-        <v>85.23</v>
+        <v>85.230000000000004</v>
       </c>
       <c r="G56" s="3">
         <v>1060.5499932</v>
@@ -7098,7 +7197,7 @@
         <v>0</v>
       </c>
       <c r="R56" s="3">
-        <v>4.42</v>
+        <v>4.4199999999999999</v>
       </c>
       <c r="S56" s="3">
         <v>0</v>
@@ -7137,7 +7236,7 @@
         <v>5.21</v>
       </c>
       <c r="AE56" s="1">
-        <v>7.92</v>
+        <v>7.9199999999999999</v>
       </c>
       <c r="AF56" s="1">
         <v>20</v>
@@ -7164,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -7178,13 +7277,13 @@
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>72.09</v>
+        <v>72.090000000000003</v>
       </c>
       <c r="F57" s="1">
         <v>14.31</v>
       </c>
       <c r="G57" s="1">
-        <v>86.4</v>
+        <v>86.400000000000006</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -7241,7 +7340,7 @@
         <v>16.259999999999998</v>
       </c>
       <c r="Z57" s="3">
-        <v>86.4</v>
+        <v>86.400000000000006</v>
       </c>
       <c r="AA57" s="1">
         <v>0</v>
@@ -7285,5 +7384,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>